--- a/data/monthly/【2026年2月】月次数値.xlsx
+++ b/data/monthly/【2026年2月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="127">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -269,31 +268,162 @@
   </si>
   <si>
     <t>ももい歯科クリニック</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>錦糸町矯正歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -301,36 +431,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -619,14 +749,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y33"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y62"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -753,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -803,7 +930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -853,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -879,10 +1006,10 @@
         <v>2584</v>
       </c>
       <c r="I5">
-        <v>1.48452</v>
+        <v>1.4845200000000001</v>
       </c>
       <c r="J5">
-        <v>55.14814815</v>
+        <v>55.148148149999997</v>
       </c>
       <c r="K5">
         <v>320</v>
@@ -906,19 +1033,19 @@
         <v>81</v>
       </c>
       <c r="S5">
-        <v>55.148148</v>
+        <v>55.148147999999999</v>
       </c>
       <c r="T5">
-        <v>2.111575</v>
+        <v>2.1115750000000002</v>
       </c>
       <c r="U5">
         <v>92</v>
       </c>
       <c r="V5">
-        <v>2.398332</v>
+        <v>2.3983319999999999</v>
       </c>
       <c r="W5">
-        <v>48.554348</v>
+        <v>48.554347999999997</v>
       </c>
       <c r="X5">
         <v>39</v>
@@ -927,7 +1054,7 @@
         <v>114.538462</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -974,34 +1101,34 @@
         <v>2893</v>
       </c>
       <c r="P6">
-        <v>1541.652264</v>
+        <v>1541.6522640000001</v>
       </c>
       <c r="Q6">
         <v>103</v>
       </c>
       <c r="S6">
-        <v>43.300971</v>
+        <v>43.300970999999997</v>
       </c>
       <c r="T6">
-        <v>3.560318</v>
+        <v>3.5603180000000001</v>
       </c>
       <c r="U6">
         <v>117</v>
       </c>
       <c r="V6">
-        <v>4.044245</v>
+        <v>4.0442450000000001</v>
       </c>
       <c r="W6">
-        <v>38.119658</v>
+        <v>38.119658000000001</v>
       </c>
       <c r="X6">
         <v>92</v>
       </c>
       <c r="Y6">
-        <v>48.478261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>48.478261000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1030,7 +1157,7 @@
         <v>1.349896</v>
       </c>
       <c r="J7">
-        <v>52.02325581</v>
+        <v>52.023255810000002</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -1054,28 +1181,28 @@
         <v>86</v>
       </c>
       <c r="S7">
-        <v>52.023256</v>
+        <v>52.023256000000003</v>
       </c>
       <c r="T7">
-        <v>2.660068</v>
+        <v>2.6600679999999999</v>
       </c>
       <c r="U7">
         <v>94</v>
       </c>
       <c r="V7">
-        <v>2.907516</v>
+        <v>2.9075160000000002</v>
       </c>
       <c r="W7">
-        <v>47.595745</v>
+        <v>47.595745000000001</v>
       </c>
       <c r="X7">
         <v>75</v>
       </c>
       <c r="Y7">
-        <v>59.653333</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>59.653333000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1104,7 +1231,7 @@
         <v>1.547674</v>
       </c>
       <c r="J8">
-        <v>45.1010101</v>
+        <v>45.101010100000003</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1128,7 +1255,7 @@
         <v>99</v>
       </c>
       <c r="S8">
-        <v>45.10101</v>
+        <v>45.101010000000002</v>
       </c>
       <c r="T8">
         <v>2.479339</v>
@@ -1137,19 +1264,19 @@
         <v>106</v>
       </c>
       <c r="V8">
-        <v>2.654646</v>
+        <v>2.6546460000000001</v>
       </c>
       <c r="W8">
-        <v>42.122642</v>
+        <v>42.122641999999999</v>
       </c>
       <c r="X8">
         <v>86</v>
       </c>
       <c r="Y8">
-        <v>51.918605</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>51.918604999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1178,7 +1305,7 @@
         <v>1.713627</v>
       </c>
       <c r="J9">
-        <v>51.28735632</v>
+        <v>51.287356320000001</v>
       </c>
       <c r="K9">
         <v>160</v>
@@ -1196,13 +1323,13 @@
         <v>4087</v>
       </c>
       <c r="P9">
-        <v>1091.754343</v>
+        <v>1091.7543430000001</v>
       </c>
       <c r="Q9">
         <v>87</v>
       </c>
       <c r="S9">
-        <v>51.287356</v>
+        <v>51.287356000000003</v>
       </c>
       <c r="T9">
         <v>2.128701</v>
@@ -1211,10 +1338,10 @@
         <v>105</v>
       </c>
       <c r="V9">
-        <v>2.569122</v>
+        <v>2.5691220000000001</v>
       </c>
       <c r="W9">
-        <v>42.495238</v>
+        <v>42.495238000000001</v>
       </c>
       <c r="X9">
         <v>71</v>
@@ -1223,7 +1350,7 @@
         <v>62.84507</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1249,7 +1376,7 @@
         <v>3434</v>
       </c>
       <c r="I10">
-        <v>1.37187</v>
+        <v>1.3718699999999999</v>
       </c>
       <c r="J10">
         <v>32.83823529</v>
@@ -1276,28 +1403,28 @@
         <v>136</v>
       </c>
       <c r="S10">
-        <v>32.838235</v>
+        <v>32.838234999999997</v>
       </c>
       <c r="T10">
-        <v>2.886861</v>
+        <v>2.8868610000000001</v>
       </c>
       <c r="U10">
         <v>166</v>
       </c>
       <c r="V10">
-        <v>3.523668</v>
+        <v>3.5236679999999998</v>
       </c>
       <c r="W10">
-        <v>26.903614</v>
+        <v>26.903614000000001</v>
       </c>
       <c r="X10">
         <v>120</v>
       </c>
       <c r="Y10">
-        <v>37.216667</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>37.216667000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1326,7 +1453,7 @@
         <v>1.354217</v>
       </c>
       <c r="J11">
-        <v>36.08064516</v>
+        <v>36.080645160000003</v>
       </c>
       <c r="K11">
         <v>160</v>
@@ -1344,22 +1471,22 @@
         <v>5620</v>
       </c>
       <c r="P11">
-        <v>796.085409</v>
+        <v>796.08540900000003</v>
       </c>
       <c r="Q11">
         <v>124</v>
       </c>
       <c r="S11">
-        <v>36.080645</v>
+        <v>36.080644999999997</v>
       </c>
       <c r="T11">
-        <v>2.206406</v>
+        <v>2.2064059999999999</v>
       </c>
       <c r="U11">
         <v>150</v>
       </c>
       <c r="V11">
-        <v>2.669039</v>
+        <v>2.6690390000000002</v>
       </c>
       <c r="W11">
         <v>29.826667</v>
@@ -1368,10 +1495,10 @@
         <v>111</v>
       </c>
       <c r="Y11">
-        <v>40.306306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>40.306305999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1397,10 +1524,10 @@
         <v>5422</v>
       </c>
       <c r="I12">
-        <v>1.309295</v>
+        <v>1.3092950000000001</v>
       </c>
       <c r="J12">
-        <v>34.3557047</v>
+        <v>34.355704699999997</v>
       </c>
       <c r="K12" t="s">
         <v>34</v>
@@ -1418,16 +1545,16 @@
         <v>7099</v>
       </c>
       <c r="P12">
-        <v>721.087477</v>
+        <v>721.08747700000004</v>
       </c>
       <c r="Q12">
         <v>127</v>
       </c>
       <c r="S12">
-        <v>40.307087</v>
+        <v>40.307087000000003</v>
       </c>
       <c r="T12">
-        <v>1.788984</v>
+        <v>1.7889839999999999</v>
       </c>
       <c r="U12">
         <v>185</v>
@@ -1436,7 +1563,7 @@
         <v>2.606001</v>
       </c>
       <c r="W12">
-        <v>27.67027</v>
+        <v>27.670269999999999</v>
       </c>
       <c r="X12">
         <v>149</v>
@@ -1445,7 +1572,7 @@
         <v>34.355705</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1474,7 +1601,7 @@
         <v>1.553191</v>
       </c>
       <c r="J13">
-        <v>66.87209302</v>
+        <v>66.872093019999994</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
@@ -1492,7 +1619,7 @@
         <v>3869</v>
       </c>
       <c r="P13">
-        <v>1486.430602</v>
+        <v>1486.4306019999999</v>
       </c>
       <c r="Q13">
         <v>97</v>
@@ -1501,25 +1628,25 @@
         <v>59.28866</v>
       </c>
       <c r="T13">
-        <v>2.507108</v>
+        <v>2.5071080000000001</v>
       </c>
       <c r="U13">
         <v>109</v>
       </c>
       <c r="V13">
-        <v>2.817265</v>
+        <v>2.8172649999999999</v>
       </c>
       <c r="W13">
-        <v>52.761468</v>
+        <v>52.761468000000001</v>
       </c>
       <c r="X13">
         <v>86</v>
       </c>
       <c r="Y13">
-        <v>66.872093</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>66.872093000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1548,7 +1675,7 @@
         <v>1.793587</v>
       </c>
       <c r="J14">
-        <v>44.94067797</v>
+        <v>44.940677970000003</v>
       </c>
       <c r="K14" t="s">
         <v>34</v>
@@ -1566,7 +1693,7 @@
         <v>6265</v>
       </c>
       <c r="P14">
-        <v>846.448524</v>
+        <v>846.44852400000002</v>
       </c>
       <c r="Q14">
         <v>132</v>
@@ -1575,25 +1702,25 @@
         <v>40.174242</v>
       </c>
       <c r="T14">
-        <v>2.106943</v>
+        <v>2.1069429999999998</v>
       </c>
       <c r="U14">
         <v>138</v>
       </c>
       <c r="V14">
-        <v>2.202713</v>
+        <v>2.2027130000000001</v>
       </c>
       <c r="W14">
-        <v>38.427536</v>
+        <v>38.427536000000003</v>
       </c>
       <c r="X14">
         <v>118</v>
       </c>
       <c r="Y14">
-        <v>44.940678</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>44.940677999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1619,10 +1746,10 @@
         <v>3720</v>
       </c>
       <c r="I15">
-        <v>1.36828</v>
+        <v>1.3682799999999999</v>
       </c>
       <c r="J15">
-        <v>43.60465116</v>
+        <v>43.604651160000003</v>
       </c>
       <c r="K15" t="s">
         <v>34</v>
@@ -1640,34 +1767,34 @@
         <v>5090</v>
       </c>
       <c r="P15">
-        <v>1105.108055</v>
+        <v>1105.1080549999999</v>
       </c>
       <c r="Q15">
         <v>129</v>
       </c>
       <c r="S15">
-        <v>43.604651</v>
+        <v>43.604650999999997</v>
       </c>
       <c r="T15">
-        <v>2.534381</v>
+        <v>2.5343810000000002</v>
       </c>
       <c r="U15">
         <v>143</v>
       </c>
       <c r="V15">
-        <v>2.80943</v>
+        <v>2.8094299999999999</v>
       </c>
       <c r="W15">
-        <v>39.335664</v>
+        <v>39.335664000000001</v>
       </c>
       <c r="X15">
         <v>129</v>
       </c>
       <c r="Y15">
-        <v>43.604651</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>43.604650999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1693,10 +1820,10 @@
         <v>3461</v>
       </c>
       <c r="I16">
-        <v>1.314938</v>
+        <v>1.3149379999999999</v>
       </c>
       <c r="J16">
-        <v>69.35555556</v>
+        <v>69.355555559999999</v>
       </c>
       <c r="K16" t="s">
         <v>34</v>
@@ -1720,7 +1847,7 @@
         <v>104</v>
       </c>
       <c r="S16">
-        <v>60.019231</v>
+        <v>60.019230999999998</v>
       </c>
       <c r="T16">
         <v>2.285212</v>
@@ -1729,19 +1856,19 @@
         <v>115</v>
       </c>
       <c r="V16">
-        <v>2.526917</v>
+        <v>2.5269170000000001</v>
       </c>
       <c r="W16">
-        <v>54.278261</v>
+        <v>54.278261000000001</v>
       </c>
       <c r="X16">
         <v>90</v>
       </c>
       <c r="Y16">
-        <v>69.355556</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>69.355556000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1767,10 +1894,10 @@
         <v>3827</v>
       </c>
       <c r="I17">
-        <v>1.246668</v>
+        <v>1.2466680000000001</v>
       </c>
       <c r="J17">
-        <v>66.20454545</v>
+        <v>66.204545449999998</v>
       </c>
       <c r="K17" t="s">
         <v>34</v>
@@ -1788,34 +1915,34 @@
         <v>4771</v>
       </c>
       <c r="P17">
-        <v>1221.127646</v>
+        <v>1221.1276459999999</v>
       </c>
       <c r="Q17">
         <v>111</v>
       </c>
       <c r="S17">
-        <v>52.486486</v>
+        <v>52.486485999999999</v>
       </c>
       <c r="T17">
-        <v>2.326556</v>
+        <v>2.3265560000000001</v>
       </c>
       <c r="U17">
         <v>121</v>
       </c>
       <c r="V17">
-        <v>2.536156</v>
+        <v>2.5361560000000001</v>
       </c>
       <c r="W17">
-        <v>48.14876</v>
+        <v>48.148760000000003</v>
       </c>
       <c r="X17">
         <v>88</v>
       </c>
       <c r="Y17">
-        <v>66.204545</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>66.204544999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1844,7 +1971,7 @@
         <v>1.491501</v>
       </c>
       <c r="J18">
-        <v>56.12244898</v>
+        <v>56.122448980000001</v>
       </c>
       <c r="K18" t="s">
         <v>34</v>
@@ -1862,34 +1989,34 @@
         <v>5089</v>
       </c>
       <c r="P18">
-        <v>1080.762429</v>
+        <v>1080.7624290000001</v>
       </c>
       <c r="Q18">
         <v>99</v>
       </c>
       <c r="S18">
-        <v>55.555556</v>
+        <v>55.555556000000003</v>
       </c>
       <c r="T18">
-        <v>1.945372</v>
+        <v>1.9453720000000001</v>
       </c>
       <c r="U18">
         <v>107</v>
       </c>
       <c r="V18">
-        <v>2.102574</v>
+        <v>2.1025740000000002</v>
       </c>
       <c r="W18">
-        <v>51.401869</v>
+        <v>51.401868999999998</v>
       </c>
       <c r="X18">
         <v>98</v>
       </c>
       <c r="Y18">
-        <v>56.122449</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>56.122449000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1939,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1986,7 +2113,7 @@
         <v>6018</v>
       </c>
       <c r="P20">
-        <v>904.785643</v>
+        <v>904.78564300000005</v>
       </c>
       <c r="Q20">
         <v>120</v>
@@ -1995,25 +2122,25 @@
         <v>45.375</v>
       </c>
       <c r="T20">
-        <v>1.994018</v>
+        <v>1.9940180000000001</v>
       </c>
       <c r="U20">
         <v>169</v>
       </c>
       <c r="V20">
-        <v>2.808242</v>
+        <v>2.8082419999999999</v>
       </c>
       <c r="W20">
-        <v>32.218935</v>
+        <v>32.218935000000002</v>
       </c>
       <c r="X20">
         <v>129</v>
       </c>
       <c r="Y20">
-        <v>42.209302</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>42.209302000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2039,10 +2166,10 @@
         <v>3274</v>
       </c>
       <c r="I21">
-        <v>1.650275</v>
+        <v>1.6502749999999999</v>
       </c>
       <c r="J21">
-        <v>45.64516129</v>
+        <v>45.645161289999997</v>
       </c>
       <c r="K21" t="s">
         <v>34</v>
@@ -2066,28 +2193,28 @@
         <v>139</v>
       </c>
       <c r="S21">
-        <v>40.719424</v>
+        <v>40.719423999999997</v>
       </c>
       <c r="T21">
-        <v>2.572645</v>
+        <v>2.5726450000000001</v>
       </c>
       <c r="U21">
         <v>166</v>
       </c>
       <c r="V21">
-        <v>3.072367</v>
+        <v>3.0723669999999998</v>
       </c>
       <c r="W21">
-        <v>34.096386</v>
+        <v>34.096386000000003</v>
       </c>
       <c r="X21">
         <v>124</v>
       </c>
       <c r="Y21">
-        <v>45.645161</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>45.645161000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2113,7 +2240,7 @@
         <v>3873</v>
       </c>
       <c r="I22">
-        <v>1.447715</v>
+        <v>1.4477150000000001</v>
       </c>
       <c r="J22">
         <v>62.5</v>
@@ -2134,25 +2261,25 @@
         <v>5607</v>
       </c>
       <c r="P22">
-        <v>980.916711</v>
+        <v>980.91671099999996</v>
       </c>
       <c r="Q22">
         <v>95</v>
       </c>
       <c r="S22">
-        <v>57.894737</v>
+        <v>57.894736999999999</v>
       </c>
       <c r="T22">
-        <v>1.694311</v>
+        <v>1.6943109999999999</v>
       </c>
       <c r="U22">
         <v>121</v>
       </c>
       <c r="V22">
-        <v>2.158017</v>
+        <v>2.1580170000000001</v>
       </c>
       <c r="W22">
-        <v>45.454545</v>
+        <v>45.454545000000003</v>
       </c>
       <c r="X22">
         <v>88</v>
@@ -2161,7 +2288,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2187,10 +2314,10 @@
         <v>2726</v>
       </c>
       <c r="I23">
-        <v>2.073001</v>
+        <v>2.0730010000000001</v>
       </c>
       <c r="J23">
-        <v>79.54166667</v>
+        <v>79.541666669999998</v>
       </c>
       <c r="K23" t="s">
         <v>34</v>
@@ -2226,16 +2353,16 @@
         <v>1.504159</v>
       </c>
       <c r="W23">
-        <v>67.376471</v>
+        <v>67.376470999999995</v>
       </c>
       <c r="X23">
         <v>72</v>
       </c>
       <c r="Y23">
-        <v>79.541667</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>79.541667000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2288,7 +2415,7 @@
         <v>109</v>
       </c>
       <c r="S24">
-        <v>49.495413</v>
+        <v>49.495412999999999</v>
       </c>
       <c r="T24">
         <v>1.954105</v>
@@ -2297,19 +2424,19 @@
         <v>134</v>
       </c>
       <c r="V24">
-        <v>2.402295</v>
+        <v>2.4022950000000001</v>
       </c>
       <c r="W24">
-        <v>40.261194</v>
+        <v>40.261194000000003</v>
       </c>
       <c r="X24">
         <v>107</v>
       </c>
       <c r="Y24">
-        <v>50.420561</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>50.420560999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2335,10 +2462,10 @@
         <v>2656</v>
       </c>
       <c r="I25">
-        <v>1.504142</v>
+        <v>1.5041420000000001</v>
       </c>
       <c r="J25">
-        <v>30.42105263</v>
+        <v>30.421052629999998</v>
       </c>
       <c r="K25" t="s">
         <v>34</v>
@@ -2365,25 +2492,25 @@
         <v>30.104167</v>
       </c>
       <c r="T25">
-        <v>4.806008</v>
+        <v>4.8060080000000003</v>
       </c>
       <c r="U25">
         <v>221</v>
       </c>
       <c r="V25">
-        <v>5.531915</v>
+        <v>5.5319149999999997</v>
       </c>
       <c r="W25">
-        <v>26.153846</v>
+        <v>26.153846000000001</v>
       </c>
       <c r="X25">
         <v>190</v>
       </c>
       <c r="Y25">
-        <v>30.421053</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>30.421053000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2409,7 +2536,7 @@
         <v>3666</v>
       </c>
       <c r="I26">
-        <v>1.740589</v>
+        <v>1.7405889999999999</v>
       </c>
       <c r="J26">
         <v>67.5</v>
@@ -2430,7 +2557,7 @@
         <v>6381</v>
       </c>
       <c r="P26">
-        <v>930.888575</v>
+        <v>930.88857499999995</v>
       </c>
       <c r="Q26">
         <v>90</v>
@@ -2439,16 +2566,16 @@
         <v>66</v>
       </c>
       <c r="T26">
-        <v>1.410437</v>
+        <v>1.4104369999999999</v>
       </c>
       <c r="U26">
         <v>113</v>
       </c>
       <c r="V26">
-        <v>1.770882</v>
+        <v>1.7708820000000001</v>
       </c>
       <c r="W26">
-        <v>52.566372</v>
+        <v>52.566372000000001</v>
       </c>
       <c r="X26">
         <v>88</v>
@@ -2457,7 +2584,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2486,7 +2613,7 @@
         <v>1.579537</v>
       </c>
       <c r="J27">
-        <v>48.1031746</v>
+        <v>48.103174600000003</v>
       </c>
       <c r="K27" t="s">
         <v>34</v>
@@ -2510,7 +2637,7 @@
         <v>130</v>
       </c>
       <c r="S27">
-        <v>46.623077</v>
+        <v>46.623077000000002</v>
       </c>
       <c r="T27">
         <v>3.073286</v>
@@ -2519,7 +2646,7 @@
         <v>141</v>
       </c>
       <c r="V27">
-        <v>3.333333</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="W27">
         <v>42.985816</v>
@@ -2531,7 +2658,7 @@
         <v>48.103175</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2557,10 +2684,10 @@
         <v>4003</v>
       </c>
       <c r="I28">
-        <v>1.724956</v>
+        <v>1.7249559999999999</v>
       </c>
       <c r="J28">
-        <v>38.03424658</v>
+        <v>38.034246580000001</v>
       </c>
       <c r="K28" t="s">
         <v>34</v>
@@ -2578,34 +2705,34 @@
         <v>6905</v>
       </c>
       <c r="P28">
-        <v>804.199855</v>
+        <v>804.19985499999996</v>
       </c>
       <c r="Q28">
         <v>104</v>
       </c>
       <c r="S28">
-        <v>53.394231</v>
+        <v>53.394230999999998</v>
       </c>
       <c r="T28">
-        <v>1.506155</v>
+        <v>1.5061549999999999</v>
       </c>
       <c r="U28">
         <v>172</v>
       </c>
       <c r="V28">
-        <v>2.490949</v>
+        <v>2.4909490000000001</v>
       </c>
       <c r="W28">
-        <v>32.284884</v>
+        <v>32.284883999999998</v>
       </c>
       <c r="X28">
         <v>146</v>
       </c>
       <c r="Y28">
-        <v>38.034247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+        <v>38.034247000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2631,10 +2758,10 @@
         <v>2538</v>
       </c>
       <c r="I29">
-        <v>1.468479</v>
+        <v>1.4684790000000001</v>
       </c>
       <c r="J29">
-        <v>37.22857143</v>
+        <v>37.228571430000002</v>
       </c>
       <c r="K29" t="s">
         <v>34</v>
@@ -2652,34 +2779,34 @@
         <v>3727</v>
       </c>
       <c r="P29">
-        <v>1048.832841</v>
+        <v>1048.8328409999999</v>
       </c>
       <c r="Q29">
         <v>107</v>
       </c>
       <c r="S29">
-        <v>36.53271</v>
+        <v>36.532710000000002</v>
       </c>
       <c r="T29">
-        <v>2.870942</v>
+        <v>2.8709419999999999</v>
       </c>
       <c r="U29">
         <v>136</v>
       </c>
       <c r="V29">
-        <v>3.649047</v>
+        <v>3.6490469999999999</v>
       </c>
       <c r="W29">
-        <v>28.742647</v>
+        <v>28.742647000000002</v>
       </c>
       <c r="X29">
         <v>105</v>
       </c>
       <c r="Y29">
-        <v>37.228571</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>37.228571000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2705,10 +2832,10 @@
         <v>3397</v>
       </c>
       <c r="I30">
-        <v>1.539888</v>
+        <v>1.5398879999999999</v>
       </c>
       <c r="J30">
-        <v>20.17741935</v>
+        <v>20.177419350000001</v>
       </c>
       <c r="K30" t="s">
         <v>34</v>
@@ -2726,13 +2853,13 @@
         <v>5231</v>
       </c>
       <c r="P30">
-        <v>717.453642</v>
+        <v>717.45364199999995</v>
       </c>
       <c r="Q30">
         <v>189</v>
       </c>
       <c r="S30">
-        <v>19.857143</v>
+        <v>19.857143000000001</v>
       </c>
       <c r="T30">
         <v>3.613076</v>
@@ -2753,7 +2880,7 @@
         <v>20.177419</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2782,7 +2909,7 @@
         <v>1.316759</v>
       </c>
       <c r="J31">
-        <v>74.52631579</v>
+        <v>74.526315789999998</v>
       </c>
       <c r="K31" t="s">
         <v>34</v>
@@ -2800,16 +2927,16 @@
         <v>3575</v>
       </c>
       <c r="P31">
-        <v>1188.251748</v>
+        <v>1188.2517479999999</v>
       </c>
       <c r="Q31">
         <v>53</v>
       </c>
       <c r="S31">
-        <v>80.150943</v>
+        <v>80.150942999999998</v>
       </c>
       <c r="T31">
-        <v>1.482517</v>
+        <v>1.4825170000000001</v>
       </c>
       <c r="U31">
         <v>57</v>
@@ -2818,16 +2945,16 @@
         <v>1.594406</v>
       </c>
       <c r="W31">
-        <v>74.526316</v>
+        <v>74.526315999999994</v>
       </c>
       <c r="X31">
         <v>57</v>
       </c>
       <c r="Y31">
-        <v>74.526316</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+        <v>74.526315999999994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2853,10 +2980,10 @@
         <v>1102</v>
       </c>
       <c r="I32">
-        <v>1.181488</v>
+        <v>1.1814880000000001</v>
       </c>
       <c r="J32">
-        <v>6.2992126</v>
+        <v>6.2992125999999997</v>
       </c>
       <c r="K32" t="s">
         <v>34</v>
@@ -2874,13 +3001,13 @@
         <v>1302</v>
       </c>
       <c r="P32">
-        <v>614.439324</v>
+        <v>614.43932400000006</v>
       </c>
       <c r="Q32">
         <v>96</v>
       </c>
       <c r="S32">
-        <v>8.333333</v>
+        <v>8.3333329999999997</v>
       </c>
       <c r="T32">
         <v>7.373272</v>
@@ -2892,7 +3019,7 @@
         <v>12.980031</v>
       </c>
       <c r="W32">
-        <v>4.733728</v>
+        <v>4.7337280000000002</v>
       </c>
       <c r="X32">
         <v>127</v>
@@ -2901,7 +3028,7 @@
         <v>6.299213</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2930,7 +3057,7 @@
         <v>1.407143</v>
       </c>
       <c r="J33">
-        <v>53.88888889</v>
+        <v>53.888888889999997</v>
       </c>
       <c r="K33" t="s">
         <v>34</v>
@@ -2954,39 +3081,2050 @@
         <v>17</v>
       </c>
       <c r="S33">
-        <v>57.058824</v>
+        <v>57.058824000000001</v>
       </c>
       <c r="T33">
-        <v>2.15736</v>
+        <v>2.1573600000000002</v>
       </c>
       <c r="U33">
         <v>22</v>
       </c>
       <c r="V33">
-        <v>2.791878</v>
+        <v>2.7918780000000001</v>
       </c>
       <c r="W33">
-        <v>44.090909</v>
+        <v>44.090909000000003</v>
       </c>
       <c r="X33">
         <v>18</v>
       </c>
       <c r="Y33">
-        <v>53.888889</v>
+        <v>53.888888999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>43</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34">
+        <v>2401</v>
+      </c>
+      <c r="I34">
+        <v>1.8154939999999999</v>
+      </c>
+      <c r="J34">
+        <v>146.62790698000001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>6305</v>
+      </c>
+      <c r="N34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34">
+        <v>4359</v>
+      </c>
+      <c r="P34">
+        <v>1446.4326679999999</v>
+      </c>
+      <c r="Q34">
+        <v>66</v>
+      </c>
+      <c r="S34">
+        <v>95.530303000000004</v>
+      </c>
+      <c r="T34">
+        <v>1.5141089999999999</v>
+      </c>
+      <c r="U34">
+        <v>85</v>
+      </c>
+      <c r="V34">
+        <v>1.949989</v>
+      </c>
+      <c r="W34">
+        <v>74.176471000000006</v>
+      </c>
+      <c r="X34">
+        <v>43</v>
+      </c>
+      <c r="Y34">
+        <v>146.62790699999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>109</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35">
+        <v>2077</v>
+      </c>
+      <c r="I35">
+        <v>1.272027</v>
+      </c>
+      <c r="J35">
+        <v>46.009174309999999</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>5015</v>
+      </c>
+      <c r="N35" t="s">
+        <v>124</v>
+      </c>
+      <c r="O35">
+        <v>2642</v>
+      </c>
+      <c r="P35">
+        <v>1898.1831950000001</v>
+      </c>
+      <c r="Q35">
+        <v>109</v>
+      </c>
+      <c r="S35">
+        <v>46.009174000000002</v>
+      </c>
+      <c r="T35">
+        <v>4.1256620000000002</v>
+      </c>
+      <c r="U35">
+        <v>117</v>
+      </c>
+      <c r="V35">
+        <v>4.4284629999999998</v>
+      </c>
+      <c r="W35">
+        <v>42.863247999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>62</v>
+      </c>
+      <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36">
+        <v>3019</v>
+      </c>
+      <c r="I36">
+        <v>1.6316660000000001</v>
+      </c>
+      <c r="J36">
+        <v>90.225806449999993</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>5594</v>
+      </c>
+      <c r="N36" t="s">
+        <v>119</v>
+      </c>
+      <c r="O36">
+        <v>4926</v>
+      </c>
+      <c r="P36">
+        <v>1135.6069829999999</v>
+      </c>
+      <c r="Q36">
+        <v>75</v>
+      </c>
+      <c r="S36">
+        <v>74.586667000000006</v>
+      </c>
+      <c r="T36">
+        <v>1.5225340000000001</v>
+      </c>
+      <c r="U36">
+        <v>79</v>
+      </c>
+      <c r="V36">
+        <v>1.6037349999999999</v>
+      </c>
+      <c r="W36">
+        <v>70.810126999999994</v>
+      </c>
+      <c r="X36">
+        <v>62</v>
+      </c>
+      <c r="Y36">
+        <v>90.225806000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37">
+        <v>68</v>
+      </c>
+      <c r="G37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37">
+        <v>4523</v>
+      </c>
+      <c r="I37">
+        <v>1.6119829999999999</v>
+      </c>
+      <c r="J37">
+        <v>65.279411760000002</v>
+      </c>
+      <c r="K37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>4439</v>
+      </c>
+      <c r="N37" t="s">
+        <v>109</v>
+      </c>
+      <c r="O37">
+        <v>7291</v>
+      </c>
+      <c r="P37">
+        <v>608.832808</v>
+      </c>
+      <c r="Q37">
+        <v>68</v>
+      </c>
+      <c r="S37">
+        <v>65.279411999999994</v>
+      </c>
+      <c r="T37">
+        <v>0.93265699999999996</v>
+      </c>
+      <c r="U37">
+        <v>76</v>
+      </c>
+      <c r="V37">
+        <v>1.042381</v>
+      </c>
+      <c r="W37">
+        <v>58.407895000000003</v>
+      </c>
+      <c r="X37">
+        <v>49</v>
+      </c>
+      <c r="Y37">
+        <v>90.591836999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38">
+        <v>2696</v>
+      </c>
+      <c r="I38">
+        <v>1.5107569999999999</v>
+      </c>
+      <c r="J38">
+        <v>83.835443040000001</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>6623</v>
+      </c>
+      <c r="N38" t="s">
+        <v>72</v>
+      </c>
+      <c r="O38">
+        <v>4073</v>
+      </c>
+      <c r="P38">
+        <v>1626.074147</v>
+      </c>
+      <c r="Q38">
+        <v>126</v>
+      </c>
+      <c r="S38">
+        <v>52.563491999999997</v>
+      </c>
+      <c r="T38">
+        <v>3.0935429999999999</v>
+      </c>
+      <c r="U38">
+        <v>142</v>
+      </c>
+      <c r="V38">
+        <v>3.4863740000000001</v>
+      </c>
+      <c r="W38">
+        <v>46.640844999999999</v>
+      </c>
+      <c r="X38">
+        <v>79</v>
+      </c>
+      <c r="Y38">
+        <v>83.835442999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>119</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40">
+        <v>2847</v>
+      </c>
+      <c r="I40">
+        <v>1.536705</v>
+      </c>
+      <c r="J40">
+        <v>57.08653846</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>5937</v>
+      </c>
+      <c r="N40" t="s">
+        <v>63</v>
+      </c>
+      <c r="O40">
+        <v>4375</v>
+      </c>
+      <c r="P40">
+        <v>1357.0285710000001</v>
+      </c>
+      <c r="Q40">
+        <v>104</v>
+      </c>
+      <c r="S40">
+        <v>57.086537999999997</v>
+      </c>
+      <c r="T40">
+        <v>2.3771429999999998</v>
+      </c>
+      <c r="U40">
+        <v>119</v>
+      </c>
+      <c r="V40">
+        <v>2.72</v>
+      </c>
+      <c r="W40">
+        <v>49.890756000000003</v>
+      </c>
+      <c r="X40">
+        <v>104</v>
+      </c>
+      <c r="Y40">
+        <v>57.086537999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>453</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41">
+        <v>8943</v>
+      </c>
+      <c r="I41">
+        <v>1.469641</v>
+      </c>
+      <c r="J41">
+        <v>49.430463580000001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>22392</v>
+      </c>
+      <c r="N41" t="s">
+        <v>116</v>
+      </c>
+      <c r="O41">
+        <v>13143</v>
+      </c>
+      <c r="P41">
+        <v>1703.7206120000001</v>
+      </c>
+      <c r="Q41">
+        <v>421</v>
+      </c>
+      <c r="S41">
+        <v>53.187648000000003</v>
+      </c>
+      <c r="T41">
+        <v>3.2032259999999999</v>
+      </c>
+      <c r="U41">
+        <v>522</v>
+      </c>
+      <c r="V41">
+        <v>3.9716960000000001</v>
+      </c>
+      <c r="W41">
+        <v>42.896552</v>
+      </c>
+      <c r="X41">
+        <v>453</v>
+      </c>
+      <c r="Y41">
+        <v>49.430464000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>85</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43">
+        <v>19</v>
+      </c>
+      <c r="G43" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43">
+        <v>2454</v>
+      </c>
+      <c r="I43">
+        <v>2.0554199999999998</v>
+      </c>
+      <c r="J43">
+        <v>285.36842104999999</v>
+      </c>
+      <c r="K43" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>5422</v>
+      </c>
+      <c r="N43" t="s">
+        <v>113</v>
+      </c>
+      <c r="O43">
+        <v>5044</v>
+      </c>
+      <c r="P43">
+        <v>1074.940523</v>
+      </c>
+      <c r="Q43">
+        <v>126</v>
+      </c>
+      <c r="S43">
+        <v>43.031745999999998</v>
+      </c>
+      <c r="T43">
+        <v>2.4980169999999999</v>
+      </c>
+      <c r="U43">
+        <v>136</v>
+      </c>
+      <c r="V43">
+        <v>2.6962730000000001</v>
+      </c>
+      <c r="W43">
+        <v>39.867646999999998</v>
+      </c>
+      <c r="X43">
+        <v>19</v>
+      </c>
+      <c r="Y43">
+        <v>285.36842100000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>3499</v>
+      </c>
+      <c r="I44">
+        <v>2.0314380000000001</v>
+      </c>
+      <c r="J44">
+        <v>61.469135799999997</v>
+      </c>
+      <c r="K44" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>4979</v>
+      </c>
+      <c r="N44" t="s">
+        <v>111</v>
+      </c>
+      <c r="O44">
+        <v>7108</v>
+      </c>
+      <c r="P44">
+        <v>700.47833400000002</v>
+      </c>
+      <c r="Q44">
+        <v>81</v>
+      </c>
+      <c r="S44">
+        <v>61.469135999999999</v>
+      </c>
+      <c r="T44">
+        <v>1.139561</v>
+      </c>
+      <c r="U44">
+        <v>99</v>
+      </c>
+      <c r="V44">
+        <v>1.3927970000000001</v>
+      </c>
+      <c r="W44">
+        <v>50.292929000000001</v>
+      </c>
+      <c r="X44">
+        <v>68</v>
+      </c>
+      <c r="Y44">
+        <v>73.220588000000006</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>125</v>
+      </c>
+      <c r="G45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45">
+        <v>2363</v>
+      </c>
+      <c r="I45">
+        <v>1.286923</v>
+      </c>
+      <c r="J45">
+        <v>38.695999999999998</v>
+      </c>
+      <c r="K45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>4837</v>
+      </c>
+      <c r="N45" t="s">
+        <v>109</v>
+      </c>
+      <c r="O45">
+        <v>3041</v>
+      </c>
+      <c r="P45">
+        <v>1590.5951990000001</v>
+      </c>
+      <c r="Q45">
+        <v>125</v>
+      </c>
+      <c r="S45">
+        <v>38.695999999999998</v>
+      </c>
+      <c r="T45">
+        <v>4.1104900000000004</v>
+      </c>
+      <c r="U45">
+        <v>149</v>
+      </c>
+      <c r="V45">
+        <v>4.8997039999999998</v>
+      </c>
+      <c r="W45">
+        <v>32.463087000000002</v>
+      </c>
+      <c r="X45">
+        <v>117</v>
+      </c>
+      <c r="Y45">
+        <v>41.341880000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>148</v>
+      </c>
+      <c r="G46" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46">
+        <v>2520</v>
+      </c>
+      <c r="I46">
+        <v>1.2964290000000001</v>
+      </c>
+      <c r="J46">
+        <v>33.195945950000002</v>
+      </c>
+      <c r="K46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>4913</v>
+      </c>
+      <c r="N46" t="s">
+        <v>96</v>
+      </c>
+      <c r="O46">
+        <v>3267</v>
+      </c>
+      <c r="P46">
+        <v>1503.8261399999999</v>
+      </c>
+      <c r="Q46">
+        <v>148</v>
+      </c>
+      <c r="S46">
+        <v>33.195945999999999</v>
+      </c>
+      <c r="T46">
+        <v>4.5301499999999999</v>
+      </c>
+      <c r="U46">
+        <v>152</v>
+      </c>
+      <c r="V46">
+        <v>4.6525860000000003</v>
+      </c>
+      <c r="W46">
+        <v>32.322367999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>88</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47">
+        <v>3510</v>
+      </c>
+      <c r="I47">
+        <v>1.6535610000000001</v>
+      </c>
+      <c r="J47">
+        <v>60.170454550000002</v>
+      </c>
+      <c r="K47" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>5295</v>
+      </c>
+      <c r="N47" t="s">
+        <v>106</v>
+      </c>
+      <c r="O47">
+        <v>5804</v>
+      </c>
+      <c r="P47">
+        <v>912.30186100000003</v>
+      </c>
+      <c r="Q47">
+        <v>88</v>
+      </c>
+      <c r="S47">
+        <v>60.170454999999997</v>
+      </c>
+      <c r="T47">
+        <v>1.5161960000000001</v>
+      </c>
+      <c r="U47">
+        <v>92</v>
+      </c>
+      <c r="V47">
+        <v>1.5851139999999999</v>
+      </c>
+      <c r="W47">
+        <v>57.554347999999997</v>
+      </c>
+      <c r="X47">
+        <v>36</v>
+      </c>
+      <c r="Y47">
+        <v>147.08333300000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>218</v>
+      </c>
+      <c r="G48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>3024</v>
+      </c>
+      <c r="I48">
+        <v>1.2103170000000001</v>
+      </c>
+      <c r="J48">
+        <v>21.958715600000001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>4787</v>
+      </c>
+      <c r="N48" t="s">
+        <v>89</v>
+      </c>
+      <c r="O48">
+        <v>3660</v>
+      </c>
+      <c r="P48">
+        <v>1307.923497</v>
+      </c>
+      <c r="Q48">
+        <v>218</v>
+      </c>
+      <c r="S48">
+        <v>21.958715999999999</v>
+      </c>
+      <c r="T48">
+        <v>5.9562840000000001</v>
+      </c>
+      <c r="U48">
+        <v>222</v>
+      </c>
+      <c r="V48">
+        <v>6.0655739999999998</v>
+      </c>
+      <c r="W48">
+        <v>21.563063</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>177</v>
+      </c>
+      <c r="G49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>2971</v>
+      </c>
+      <c r="I49">
+        <v>1.4887239999999999</v>
+      </c>
+      <c r="J49">
+        <v>28.689265540000001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>5078</v>
+      </c>
+      <c r="N49" t="s">
+        <v>103</v>
+      </c>
+      <c r="O49">
+        <v>4423</v>
+      </c>
+      <c r="P49">
+        <v>1148.089532</v>
+      </c>
+      <c r="Q49">
+        <v>177</v>
+      </c>
+      <c r="S49">
+        <v>28.689266</v>
+      </c>
+      <c r="T49">
+        <v>4.0018089999999997</v>
+      </c>
+      <c r="U49">
+        <v>201</v>
+      </c>
+      <c r="V49">
+        <v>4.5444269999999998</v>
+      </c>
+      <c r="W49">
+        <v>25.263681999999999</v>
+      </c>
+      <c r="X49">
+        <v>178</v>
+      </c>
+      <c r="Y49">
+        <v>28.528089999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50">
+        <v>67</v>
+      </c>
+      <c r="G50" t="s">
+        <v>49</v>
+      </c>
+      <c r="H50">
+        <v>992</v>
+      </c>
+      <c r="I50">
+        <v>1.264113</v>
+      </c>
+      <c r="J50">
+        <v>14.373134329999999</v>
+      </c>
+      <c r="K50" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>963</v>
+      </c>
+      <c r="N50" t="s">
+        <v>81</v>
+      </c>
+      <c r="O50">
+        <v>1254</v>
+      </c>
+      <c r="P50">
+        <v>767.94258400000001</v>
+      </c>
+      <c r="Q50">
+        <v>74</v>
+      </c>
+      <c r="S50">
+        <v>13.013514000000001</v>
+      </c>
+      <c r="T50">
+        <v>5.901116</v>
+      </c>
+      <c r="U50">
+        <v>86</v>
+      </c>
+      <c r="V50">
+        <v>6.8580540000000001</v>
+      </c>
+      <c r="W50">
+        <v>11.197673999999999</v>
+      </c>
+      <c r="X50">
+        <v>67</v>
+      </c>
+      <c r="Y50">
+        <v>14.373134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>107</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51">
+        <v>2539</v>
+      </c>
+      <c r="I51">
+        <v>1.484837</v>
+      </c>
+      <c r="J51">
+        <v>46.336448599999997</v>
+      </c>
+      <c r="K51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>4958</v>
+      </c>
+      <c r="N51" t="s">
+        <v>96</v>
+      </c>
+      <c r="O51">
+        <v>3770</v>
+      </c>
+      <c r="P51">
+        <v>1315.119363</v>
+      </c>
+      <c r="Q51">
+        <v>107</v>
+      </c>
+      <c r="S51">
+        <v>46.336449000000002</v>
+      </c>
+      <c r="T51">
+        <v>2.8381959999999999</v>
+      </c>
+      <c r="U51">
+        <v>121</v>
+      </c>
+      <c r="V51">
+        <v>3.209549</v>
+      </c>
+      <c r="W51">
+        <v>40.975206999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>121</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52">
+        <v>2888</v>
+      </c>
+      <c r="I52">
+        <v>1.377078</v>
+      </c>
+      <c r="J52">
+        <v>43.338842980000003</v>
+      </c>
+      <c r="K52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>5244</v>
+      </c>
+      <c r="N52" t="s">
+        <v>99</v>
+      </c>
+      <c r="O52">
+        <v>3977</v>
+      </c>
+      <c r="P52">
+        <v>1318.581846</v>
+      </c>
+      <c r="Q52">
+        <v>121</v>
+      </c>
+      <c r="S52">
+        <v>43.338842999999997</v>
+      </c>
+      <c r="T52">
+        <v>3.042494</v>
+      </c>
+      <c r="U52">
+        <v>171</v>
+      </c>
+      <c r="V52">
+        <v>4.2997230000000002</v>
+      </c>
+      <c r="W52">
+        <v>30.666667</v>
+      </c>
+      <c r="X52">
+        <v>130</v>
+      </c>
+      <c r="Y52">
+        <v>40.338462</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>59</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53">
+        <v>1267</v>
+      </c>
+      <c r="I53">
+        <v>3.686661</v>
+      </c>
+      <c r="J53">
+        <v>78.372881359999994</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>4624</v>
+      </c>
+      <c r="N53" t="s">
+        <v>35</v>
+      </c>
+      <c r="O53">
+        <v>4671</v>
+      </c>
+      <c r="P53">
+        <v>989.93791499999998</v>
+      </c>
+      <c r="Q53">
+        <v>59</v>
+      </c>
+      <c r="S53">
+        <v>78.372881000000007</v>
+      </c>
+      <c r="T53">
+        <v>1.2631129999999999</v>
+      </c>
+      <c r="U53">
+        <v>64</v>
+      </c>
+      <c r="V53">
+        <v>1.3701559999999999</v>
+      </c>
+      <c r="W53">
+        <v>72.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54">
+        <v>97</v>
+      </c>
+      <c r="G54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54">
+        <v>3025</v>
+      </c>
+      <c r="I54">
+        <v>1.3841319999999999</v>
+      </c>
+      <c r="J54">
+        <v>48.051546389999999</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>4661</v>
+      </c>
+      <c r="N54" t="s">
+        <v>96</v>
+      </c>
+      <c r="O54">
+        <v>4187</v>
+      </c>
+      <c r="P54">
+        <v>1113.207547</v>
+      </c>
+      <c r="Q54">
+        <v>97</v>
+      </c>
+      <c r="S54">
+        <v>48.051546000000002</v>
+      </c>
+      <c r="T54">
+        <v>2.3166950000000002</v>
+      </c>
+      <c r="U54">
+        <v>109</v>
+      </c>
+      <c r="V54">
+        <v>2.6032959999999998</v>
+      </c>
+      <c r="W54">
+        <v>42.761468000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>74</v>
+      </c>
+      <c r="G55" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55">
+        <v>3434</v>
+      </c>
+      <c r="I55">
+        <v>1.4088529999999999</v>
+      </c>
+      <c r="J55">
+        <v>64.932432430000006</v>
+      </c>
+      <c r="K55" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>4805</v>
+      </c>
+      <c r="N55" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55">
+        <v>4838</v>
+      </c>
+      <c r="P55">
+        <v>993.17899999999997</v>
+      </c>
+      <c r="Q55">
+        <v>74</v>
+      </c>
+      <c r="S55">
+        <v>64.932432000000006</v>
+      </c>
+      <c r="T55">
+        <v>1.529558</v>
+      </c>
+      <c r="U55">
+        <v>82</v>
+      </c>
+      <c r="V55">
+        <v>1.6949149999999999</v>
+      </c>
+      <c r="W55">
+        <v>58.597560999999999</v>
+      </c>
+      <c r="X55">
+        <v>50</v>
+      </c>
+      <c r="Y55">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>61</v>
+      </c>
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56">
+        <v>2342</v>
+      </c>
+      <c r="I56">
+        <v>1.2275830000000001</v>
+      </c>
+      <c r="J56">
+        <v>53.31147541</v>
+      </c>
+      <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>3252</v>
+      </c>
+      <c r="N56" t="s">
+        <v>92</v>
+      </c>
+      <c r="O56">
+        <v>2875</v>
+      </c>
+      <c r="P56">
+        <v>1131.130435</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+      <c r="S56">
+        <v>53.311475000000002</v>
+      </c>
+      <c r="T56">
+        <v>2.1217389999999998</v>
+      </c>
+      <c r="U56">
+        <v>64</v>
+      </c>
+      <c r="V56">
+        <v>2.2260870000000001</v>
+      </c>
+      <c r="W56">
+        <v>50.8125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" t="s">
+        <v>87</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>58</v>
+      </c>
+      <c r="G57" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57">
+        <v>2281</v>
+      </c>
+      <c r="I57">
+        <v>1.2595350000000001</v>
+      </c>
+      <c r="J57">
+        <v>84.534482760000003</v>
+      </c>
+      <c r="K57" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>4903</v>
+      </c>
+      <c r="N57" t="s">
+        <v>91</v>
+      </c>
+      <c r="O57">
+        <v>2873</v>
+      </c>
+      <c r="P57">
+        <v>1706.578489</v>
+      </c>
+      <c r="Q57">
+        <v>58</v>
+      </c>
+      <c r="S57">
+        <v>84.534482999999994</v>
+      </c>
+      <c r="T57">
+        <v>2.018796</v>
+      </c>
+      <c r="U57">
+        <v>59</v>
+      </c>
+      <c r="V57">
+        <v>2.0536029999999998</v>
+      </c>
+      <c r="W57">
+        <v>83.101695000000007</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58">
+        <v>68</v>
+      </c>
+      <c r="G58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58">
+        <v>2360</v>
+      </c>
+      <c r="I58">
+        <v>1.283898</v>
+      </c>
+      <c r="J58">
+        <v>71.367647059999996</v>
+      </c>
+      <c r="K58" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>4853</v>
+      </c>
+      <c r="N58" t="s">
+        <v>89</v>
+      </c>
+      <c r="O58">
+        <v>3030</v>
+      </c>
+      <c r="P58">
+        <v>1601.650165</v>
+      </c>
+      <c r="Q58">
+        <v>68</v>
+      </c>
+      <c r="S58">
+        <v>71.367647000000005</v>
+      </c>
+      <c r="T58">
+        <v>2.244224</v>
+      </c>
+      <c r="U58">
+        <v>74</v>
+      </c>
+      <c r="V58">
+        <v>2.4422440000000001</v>
+      </c>
+      <c r="W58">
+        <v>65.581080999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" t="s">
+        <v>87</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>114</v>
+      </c>
+      <c r="G59" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59">
+        <v>2385</v>
+      </c>
+      <c r="I59">
+        <v>1.3224320000000001</v>
+      </c>
+      <c r="J59">
+        <v>48.815789469999999</v>
+      </c>
+      <c r="K59" t="s">
+        <v>34</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>5565</v>
+      </c>
+      <c r="N59" t="s">
+        <v>85</v>
+      </c>
+      <c r="O59">
+        <v>3154</v>
+      </c>
+      <c r="P59">
+        <v>1764.4261260000001</v>
+      </c>
+      <c r="Q59">
+        <v>109</v>
+      </c>
+      <c r="S59">
+        <v>51.055045999999997</v>
+      </c>
+      <c r="T59">
+        <v>3.4559289999999998</v>
+      </c>
+      <c r="U59">
+        <v>129</v>
+      </c>
+      <c r="V59">
+        <v>4.0900439999999998</v>
+      </c>
+      <c r="W59">
+        <v>43.139535000000002</v>
+      </c>
+      <c r="X59">
+        <v>114</v>
+      </c>
+      <c r="Y59">
+        <v>48.815789000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
+        <v>34</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>85</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>128</v>
+      </c>
+      <c r="G61" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61">
+        <v>2875</v>
+      </c>
+      <c r="I61">
+        <v>2.0695649999999999</v>
+      </c>
+      <c r="J61">
+        <v>42.1953125</v>
+      </c>
+      <c r="K61" t="s">
+        <v>34</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>5401</v>
+      </c>
+      <c r="N61" t="s">
+        <v>72</v>
+      </c>
+      <c r="O61">
+        <v>5950</v>
+      </c>
+      <c r="P61">
+        <v>907.73109199999999</v>
+      </c>
+      <c r="Q61">
+        <v>123</v>
+      </c>
+      <c r="S61">
+        <v>43.910569000000002</v>
+      </c>
+      <c r="T61">
+        <v>2.0672269999999999</v>
+      </c>
+      <c r="U61">
+        <v>137</v>
+      </c>
+      <c r="V61">
+        <v>2.302521</v>
+      </c>
+      <c r="W61">
+        <v>39.423358</v>
+      </c>
+      <c r="X61">
+        <v>128</v>
+      </c>
+      <c r="Y61">
+        <v>42.195312999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62">
+        <v>484</v>
+      </c>
+      <c r="I62">
+        <v>1.2603310000000001</v>
+      </c>
+      <c r="J62">
+        <v>226.8</v>
+      </c>
+      <c r="K62" t="s">
+        <v>34</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>1134</v>
+      </c>
+      <c r="N62" t="s">
+        <v>81</v>
+      </c>
+      <c r="O62">
+        <v>610</v>
+      </c>
+      <c r="P62">
+        <v>1859.0163930000001</v>
+      </c>
+      <c r="Q62">
+        <v>11</v>
+      </c>
+      <c r="S62">
+        <v>103.090909</v>
+      </c>
+      <c r="T62">
+        <v>1.8032790000000001</v>
+      </c>
+      <c r="U62">
+        <v>13</v>
+      </c>
+      <c r="V62">
+        <v>2.131148</v>
+      </c>
+      <c r="W62">
+        <v>87.230768999999995</v>
+      </c>
+      <c r="X62">
+        <v>5</v>
+      </c>
+      <c r="Y62">
+        <v>226.8</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>